--- a/sheets/민요/검수/는실 타령.xlsx
+++ b/sheets/민요/검수/는실 타령.xlsx
@@ -4,15 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
-    <sheet name="악보 2" sheetId="4" r:id="rId4"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -21,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -51,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -74,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +176,57 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6076,8 +6206,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:U28"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -6100,1442 +6234,1870 @@
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">는실 타령 — 민요채보-3/는실 타령.png (1/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">는실 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+      <c s="8" r="R2"/>
+      <c s="8" r="S2"/>
+      <c s="8" r="T2"/>
+      <c s="8" r="U2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">영</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">둥</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="N3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="P3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">밤</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="R3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="S3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">둥</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="T3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">둥</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―汰</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―㳞</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">汰</t>
+          </r>
+        </is>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">㳞</t>
+          </r>
+        </is>
+      </c>
+      <c r="E4" s="19"/>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―淋</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―潢</t>
-        </is>
-      </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―淋</t>
-        </is>
-      </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―潢</t>
-        </is>
-      </c>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―汰</t>
-        </is>
-      </c>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―潢</t>
-        </is>
-      </c>
-      <c r="U4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I4" s="19"/>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">淋</t>
+          </r>
+        </is>
+      </c>
+      <c r="K4" s="19"/>
+      <c r="L4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢</t>
+          </r>
+        </is>
+      </c>
+      <c r="M4" s="19"/>
+      <c r="N4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">淋</t>
+          </r>
+        </is>
+      </c>
+      <c r="O4" s="19"/>
+      <c r="P4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">汰</t>
+          </r>
+        </is>
+      </c>
+      <c r="S4" s="19"/>
+      <c r="T4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢</t>
+          </r>
+        </is>
+      </c>
+      <c r="U4" s="19"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G5" s="20"/>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K5" s="20"/>
+      <c r="L5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M5" s="20"/>
+      <c r="N5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="P5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="S5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="T5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C6" s="18"/>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">래</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K6" s="18"/>
+      <c r="L6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M6" s="18"/>
+      <c r="N6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O6" s="18"/>
+      <c r="P6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="R6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="S6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">래</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="T6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">래</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―㳞</t>
-        </is>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―㳞</t>
-        </is>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―㳞</t>
-        </is>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―㳞</t>
-        </is>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―汰</t>
-        </is>
-      </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―潢</t>
-        </is>
-      </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―汰</t>
-        </is>
-      </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―潢</t>
-        </is>
-      </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―淋</t>
-        </is>
-      </c>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―林</t>
-        </is>
-      </c>
-      <c r="U7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">㳞</t>
+          </r>
+        </is>
+      </c>
+      <c r="C7" s="19"/>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">㳞</t>
+          </r>
+        </is>
+      </c>
+      <c r="E7" s="19"/>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">㳞</t>
+          </r>
+        </is>
+      </c>
+      <c r="G7" s="19"/>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">㳞</t>
+          </r>
+        </is>
+      </c>
+      <c r="I7" s="19"/>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">汰</t>
+          </r>
+        </is>
+      </c>
+      <c r="K7" s="19"/>
+      <c r="L7" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢</t>
+          </r>
+        </is>
+      </c>
+      <c r="M7" s="19"/>
+      <c r="N7" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">汰</t>
+          </r>
+        </is>
+      </c>
+      <c r="O7" s="19"/>
+      <c r="P7" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">淋</t>
+          </r>
+        </is>
+      </c>
+      <c r="S7" s="19"/>
+      <c r="T7" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">林</t>
+          </r>
+        </is>
+      </c>
+      <c r="U7" s="19"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C8" s="20"/>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G8" s="20"/>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">당</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K8" s="20"/>
+      <c r="L8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M8" s="20"/>
+      <c r="N8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O8" s="20"/>
+      <c r="P8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="S8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">당</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="T8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">당</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="18"/>
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" s="18"/>
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">갑</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">거</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="N9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O9" s="18"/>
+      <c r="P9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">테</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U9" s="2"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="R9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="S9" s="18"/>
+      <c r="T9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U9" s="18"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="19"/>
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="19"/>
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―潢</t>
-        </is>
-      </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―淋</t>
-        </is>
-      </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―潢</t>
-        </is>
-      </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―汰</t>
-        </is>
-      </c>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―潢</t>
-        </is>
-      </c>
-      <c r="U10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="G10" s="19"/>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I10" s="19"/>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K10" s="19"/>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢</t>
+          </r>
+        </is>
+      </c>
+      <c r="M10" s="19"/>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">淋</t>
+          </r>
+        </is>
+      </c>
+      <c r="O10" s="19"/>
+      <c r="P10" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">汰</t>
+          </r>
+        </is>
+      </c>
+      <c r="S10" s="19"/>
+      <c r="T10" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢</t>
+          </r>
+        </is>
+      </c>
+      <c r="U10" s="19"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="20"/>
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="E11" s="20"/>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G11" s="20"/>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I11" s="20"/>
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="K11" s="20"/>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M11" s="20"/>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O11" s="20"/>
+      <c r="P11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="S11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
+      <c r="T11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" s="18"/>
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E12" s="18"/>
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G12" s="18"/>
+      <c r="H12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―潢</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="I12" s="18"/>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K12" s="18"/>
+      <c r="L12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M12" s="18"/>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O12" s="18"/>
+      <c r="P12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q12" s="18"/>
+      <c r="R12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="S12" s="18"/>
+      <c r="T12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U12" s="18"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢</t>
+          </r>
+        </is>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E13" s="19"/>
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―淋</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―潢</t>
-        </is>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―汰</t>
-        </is>
-      </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―潢</t>
-        </is>
-      </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―汰</t>
-        </is>
-      </c>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―潢</t>
-        </is>
-      </c>
-      <c r="U13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U14" s="2"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">淋</t>
+          </r>
+        </is>
+      </c>
+      <c r="I13" s="19"/>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢</t>
+          </r>
+        </is>
+      </c>
+      <c r="K13" s="19"/>
+      <c r="L13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M13" s="19"/>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">汰</t>
+          </r>
+        </is>
+      </c>
+      <c r="O13" s="19"/>
+      <c r="P13" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">汰</t>
+          </r>
+        </is>
+      </c>
+      <c r="S13" s="19"/>
+      <c r="T13" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢</t>
+          </r>
+        </is>
+      </c>
+      <c r="U13" s="19"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G14" s="20"/>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I14" s="20"/>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K14" s="20"/>
+      <c r="L14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M14" s="20"/>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O14" s="20"/>
+      <c r="P14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="S14" s="20"/>
+      <c r="T14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U14" s="20"/>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">는실 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C16"/>
+      <c s="8" r="D16"/>
+      <c s="8" r="E16"/>
+      <c s="8" r="F16"/>
+      <c s="8" r="G16"/>
+      <c s="8" r="H16"/>
+      <c s="8" r="I16"/>
+      <c s="8" r="J16"/>
+      <c s="8" r="K16"/>
+      <c s="8" r="L16"/>
+      <c s="8" r="M16"/>
+      <c s="8" r="N16"/>
+      <c s="8" r="O16"/>
+      <c s="8" r="P16"/>
+      <c s="8" r="Q16"/>
+      <c s="8" r="R16"/>
+      <c s="8" r="S16"/>
+      <c s="8" r="T16"/>
+      <c s="8" r="U16"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="17"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q17" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회</t>
+        </is>
+      </c>
+      <c r="R17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="S17" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지</t>
+        </is>
+      </c>
+      <c r="T17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U17" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="17"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">㳞</t>
+          </r>
+        </is>
+      </c>
+      <c r="S18" s="19"/>
+      <c r="T18" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢</t>
+          </r>
+        </is>
+      </c>
+      <c r="U18" s="19"/>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="B19" s="17"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q19" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보</t>
+        </is>
+      </c>
+      <c r="R19" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="S19" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화</t>
+        </is>
+      </c>
+      <c r="T19" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U19" s="20"/>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="B20" s="17"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="21"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q20" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">래</t>
+        </is>
+      </c>
+      <c r="R20" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="S20" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자</t>
+        </is>
+      </c>
+      <c r="T20" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="U20" s="18"/>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="B21" s="17"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">㳞</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">㳞</t>
+          </r>
+        </is>
+      </c>
+      <c r="S21" s="19"/>
+      <c r="T21" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">㳞</t>
+          </r>
+        </is>
+      </c>
+      <c r="U21" s="19"/>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="B22" s="17"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q22" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대</t>
+        </is>
+      </c>
+      <c r="R22" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="S22" s="20"/>
+      <c r="T22" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="U22" s="20"/>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="B23" s="17"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="21"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">林</t>
+        </is>
+      </c>
+      <c r="Q23" s="18"/>
+      <c r="R23" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">林</t>
+        </is>
+      </c>
+      <c r="S23" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좋</t>
+        </is>
+      </c>
+      <c r="T23" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">林</t>
+        </is>
+      </c>
+      <c r="U23" s="18"/>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="B24" s="17"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">林</t>
+        </is>
+      </c>
+      <c r="S24" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
+      <c r="T24" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U24" s="19"/>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="B25" s="17"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="23"/>
+      <c r="P25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="S25" s="20"/>
+      <c r="T25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢汰</t>
+        </is>
+      </c>
+      <c r="U25" s="20"/>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="B26" s="17"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">淋</t>
+        </is>
+      </c>
+      <c r="Q26" s="18"/>
+      <c r="R26" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">淋</t>
+        </is>
+      </c>
+      <c r="S26" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">씨</t>
+        </is>
+      </c>
+      <c r="T26" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">淋</t>
+        </is>
+      </c>
+      <c r="U26" s="18"/>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="B27" s="17"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢汰</t>
+        </is>
+      </c>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢汰</t>
+        </is>
+      </c>
+      <c r="S27" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구</t>
+        </is>
+      </c>
+      <c r="T27" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢汰</t>
+        </is>
+      </c>
+      <c r="U27" s="19"/>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="B28" s="17"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S28" s="20"/>
+      <c r="T28" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U28" s="20"/>
     </row>
   </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">는실 타령 — 민요채보-3/는실 타령.png (2/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">지</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">단</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―潢</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―㳞</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―潢</t>
-        </is>
-      </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">화</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">래</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―㳞</t>
-        </is>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―㳞</t>
-        </is>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―㳞</t>
-        </is>
-      </c>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">林</t>
-        </is>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">林</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">좋</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">林</t>
-        </is>
-      </c>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">林</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">을</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">씨</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">구</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-    </row>
-  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:U2"/>
+    <mergeCell ref="B16:U16"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="61"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="14" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
--- a/sheets/민요/검수/는실 타령.xlsx
+++ b/sheets/민요/검수/는실 타령.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -553,13 +553,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―林|姑</t>
+          <t xml:space="preserve">姑|–林|姑</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―林
+–林
 姑</t>
         </is>
       </c>
@@ -594,13 +594,13 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―潢南</t>
+          <t xml:space="preserve">姑|–潢南</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―潢南</t>
+–潢南</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -634,13 +634,13 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―林|姑</t>
+          <t xml:space="preserve">姑|–林|姑</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―林
+–林
 姑</t>
         </is>
       </c>
@@ -675,13 +675,13 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―潢南</t>
+          <t xml:space="preserve">姑|–潢南</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―潢南</t>
+–潢南</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -715,13 +715,13 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―淋|姑</t>
+          <t xml:space="preserve">潢|–淋|姑</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―淋
+–淋
 姑</t>
         </is>
       </c>
@@ -799,13 +799,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―潢南</t>
+          <t xml:space="preserve">姑|–潢南</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―潢南</t>
+–潢南</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -839,13 +839,13 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―淋汰</t>
+          <t xml:space="preserve">潢|–淋汰</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―淋汰</t>
+–淋汰</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -883,13 +883,13 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―淋潢</t>
+          <t xml:space="preserve">潢|–淋潢</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―淋潢</t>
+–淋潢</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -970,13 +970,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢</t>
+          <t xml:space="preserve">–潢</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢</t>
+          <t xml:space="preserve">–潢</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1132,13 +1132,13 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―汰黃</t>
+          <t xml:space="preserve">潢|–汰黃</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰黃</t>
+–汰黃</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1219,13 +1219,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1302,13 +1302,13 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―潢</t>
+          <t xml:space="preserve">姑|–潢</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1424,13 +1424,13 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―姑</t>
+          <t xml:space="preserve">姑|–姑</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1503,13 +1503,13 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1547,13 +1547,13 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―淋</t>
+          <t xml:space="preserve">潢|–淋</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―淋</t>
+–淋</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1587,13 +1587,13 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―汰潢</t>
+          <t xml:space="preserve">潢|–汰潢</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰潢</t>
+–汰潢</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -1631,13 +1631,13 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―汰淋汰</t>
+          <t xml:space="preserve">潢|–汰淋汰</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰淋汰</t>
+–汰淋汰</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -1675,13 +1675,13 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -1719,13 +1719,13 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―汰黃汰</t>
+          <t xml:space="preserve">潢|–汰黃汰</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰黃汰</t>
+–汰黃汰</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -1849,13 +1849,13 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋|―淋汰</t>
+          <t xml:space="preserve">淋|–淋汰</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-―淋汰</t>
+–淋汰</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -1893,13 +1893,13 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―汰汰</t>
+          <t xml:space="preserve">潢|–汰汰</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰汰</t>
+–汰汰</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -1980,13 +1980,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2020,13 +2020,13 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2060,13 +2060,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―淋</t>
+          <t xml:space="preserve">潢|–淋</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―淋</t>
+–淋</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2100,13 +2100,13 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―汰潢</t>
+          <t xml:space="preserve">潢|–汰潢</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰潢</t>
+–汰潢</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -2144,13 +2144,13 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―汰淋汰</t>
+          <t xml:space="preserve">潢|–汰淋汰</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰淋汰</t>
+–汰淋汰</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -2188,13 +2188,13 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -2232,13 +2232,13 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2272,12 +2272,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2311,13 +2311,13 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―潢黃</t>
+          <t xml:space="preserve">姑|–潢黃</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―潢黃</t>
+–潢黃</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -2398,13 +2398,13 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―姑</t>
+          <t xml:space="preserve">姑|–姑</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2477,12 +2477,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2516,13 +2516,13 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -2560,13 +2560,13 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―潢</t>
+          <t xml:space="preserve">姑|–潢</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2600,13 +2600,13 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―淋</t>
+          <t xml:space="preserve">潢|–淋</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―淋</t>
+–淋</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -2722,13 +2722,13 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―汰潢</t>
+          <t xml:space="preserve">潢|–汰潢</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰潢</t>
+–汰潢</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -2766,13 +2766,13 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―潢汰潢</t>
+          <t xml:space="preserve">姑|–潢汰潢</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―潢汰潢</t>
+–潢汰潢</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I57" s="2"/>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="I59" s="2"/>
@@ -3067,12 +3067,12 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢黃</t>
+          <t xml:space="preserve">–潢黃</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢黃</t>
+          <t xml:space="preserve">–潢黃</t>
         </is>
       </c>
       <c r="I63" s="2"/>
@@ -3172,13 +3172,13 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―汰潢</t>
+          <t xml:space="preserve">潢|–汰潢</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰潢</t>
+–汰潢</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -3216,13 +3216,13 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―潢汰</t>
+          <t xml:space="preserve">姑|–潢汰</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―潢汰</t>
+–潢汰</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I68" s="2"/>
@@ -3295,12 +3295,12 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I69" s="2"/>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="I71" s="2"/>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢黃</t>
+          <t xml:space="preserve">–潢黃</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢黃</t>
+          <t xml:space="preserve">–潢黃</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I83" s="2"/>
@@ -3861,12 +3861,12 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I84" s="2"/>
@@ -3983,7 +3983,7 @@
       <c r="F3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
@@ -3994,7 +3994,7 @@
       <c r="H3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―淋</t>
+–淋</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
@@ -4005,7 +4005,7 @@
       <c r="J3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―淋</t>
+–淋</t>
         </is>
       </c>
       <c r="K3" s="8" t="inlineStr">
@@ -4027,7 +4027,7 @@
       <c r="N3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―林
+–林
 姑</t>
         </is>
       </c>
@@ -4041,7 +4041,7 @@
       <c r="A4" s="0"/>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢黃</t>
+          <t xml:space="preserve">–潢黃</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -4051,14 +4051,14 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢黃</t>
+          <t xml:space="preserve">–潢黃</t>
         </is>
       </c>
       <c r="E4" s="9"/>
       <c r="F4" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―淋</t>
+–淋</t>
         </is>
       </c>
       <c r="G4" s="12" t="inlineStr">
@@ -4069,7 +4069,7 @@
       <c r="H4" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰潢</t>
+–汰潢</t>
         </is>
       </c>
       <c r="I4" s="12" t="inlineStr">
@@ -4080,7 +4080,7 @@
       <c r="J4" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰潢</t>
+–汰潢</t>
         </is>
       </c>
       <c r="K4" s="12" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="L4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢</t>
+          <t xml:space="preserve">–潢</t>
         </is>
       </c>
       <c r="M4" s="9" t="inlineStr">
@@ -4101,7 +4101,7 @@
       <c r="N4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―潢南</t>
+–潢南</t>
         </is>
       </c>
       <c r="O4" s="9" t="inlineStr">
@@ -4141,7 +4141,7 @@
       <c r="H5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰淋汰</t>
+–汰淋汰</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -4152,7 +4152,7 @@
       <c r="J5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰淋汰</t>
+–汰淋汰</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -4163,7 +4163,7 @@
       <c r="L5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰黃</t>
+–汰黃</t>
         </is>
       </c>
       <c r="M5" s="13" t="inlineStr">
@@ -4174,7 +4174,7 @@
       <c r="N5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―林
+–林
 姑</t>
         </is>
       </c>
@@ -4215,7 +4215,7 @@
       <c r="H6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -4226,7 +4226,7 @@
       <c r="J6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
@@ -4247,7 +4247,7 @@
       <c r="N6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―潢南</t>
+–潢南</t>
         </is>
       </c>
       <c r="O6" s="8" t="inlineStr">
@@ -4260,7 +4260,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -4271,7 +4271,7 @@
       <c r="D7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰潢</t>
+–汰潢</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -4282,7 +4282,7 @@
       <c r="F7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰潢</t>
+–汰潢</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
@@ -4293,7 +4293,7 @@
       <c r="H7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -4304,7 +4304,7 @@
       <c r="J7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰黃汰</t>
+–汰黃汰</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
@@ -4315,7 +4315,7 @@
       <c r="L7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr">
@@ -4326,7 +4326,7 @@
       <c r="N7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―淋
+–淋
 姑</t>
         </is>
       </c>
@@ -4351,7 +4351,7 @@
       <c r="D8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―潢汰</t>
+–潢汰</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -4362,7 +4362,7 @@
       <c r="F8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―潢汰潢</t>
+–潢汰潢</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
@@ -4415,7 +4415,7 @@
       <c r="A9" s="0"/>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -4425,13 +4425,13 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -4442,7 +4442,7 @@
       <c r="H9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―潢黃</t>
+–潢黃</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
@@ -4463,7 +4463,7 @@
       <c r="L9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr">
@@ -4474,7 +4474,7 @@
       <c r="N9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―潢南</t>
+–潢南</t>
         </is>
       </c>
       <c r="O9" s="8" t="inlineStr">
@@ -4497,13 +4497,13 @@
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G10" s="9"/>
@@ -4520,7 +4520,7 @@
       <c r="J10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-―淋汰</t>
+–淋汰</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
@@ -4541,7 +4541,7 @@
       <c r="N10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―淋汰</t>
+–淋汰</t>
         </is>
       </c>
       <c r="O10" s="12" t="inlineStr">
@@ -4554,7 +4554,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -4577,7 +4577,7 @@
       <c r="H11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
@@ -4588,7 +4588,7 @@
       <c r="J11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰汰</t>
+–汰汰</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
@@ -4609,7 +4609,7 @@
       <c r="N11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―淋潢</t>
+–淋潢</t>
         </is>
       </c>
       <c r="O11" s="13" t="inlineStr">
@@ -4622,19 +4622,19 @@
       <c r="A12" s="0"/>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="G12" s="8"/>
@@ -4661,7 +4661,7 @@
       <c r="L12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
@@ -4684,7 +4684,7 @@
       <c r="A13" s="0"/>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C13" s="9"/>
@@ -4702,7 +4702,7 @@
       <c r="G13" s="9"/>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -4713,7 +4713,7 @@
       <c r="J13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
@@ -4734,7 +4734,7 @@
       <c r="N13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="O13" s="9" t="inlineStr">
@@ -4766,7 +4766,7 @@
       <c r="H14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
@@ -4777,7 +4777,7 @@
       <c r="J14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="K14" s="10" t="inlineStr">
@@ -4788,7 +4788,7 @@
       <c r="L14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="M14" s="13" t="inlineStr">

--- a/sheets/민요/검수/는실 타령.xlsx
+++ b/sheets/민요/검수/는실 타령.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3938,100 +3979,100 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">는실 타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃黃
 ·</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">얼씨</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑潢潢</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –潢</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">달</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –淋</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">희오</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –淋</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">핫</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 ··</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">백</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –林
 姑</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">둥</t>
         </is>
@@ -4039,72 +4080,72 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–潢黃</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–潢黃</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="E4" s="25"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –淋</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H4" s="18" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –汰潢</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="I4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">래</t>
         </is>
       </c>
-      <c r="J4" s="18" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –汰潢</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="K4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–潢</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">몽</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –潢南</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">그래</t>
         </is>
@@ -4112,73 +4153,73 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="27"/>
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –汰淋汰</t>
         </is>
       </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="I5" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">사장</t>
         </is>
       </c>
-      <c r="J5" s="18" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –汰淋汰</t>
         </is>
       </c>
-      <c r="K5" s="13" t="inlineStr">
+      <c r="K5" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="L5" s="18" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –汰黃</t>
         </is>
       </c>
-      <c r="M5" s="13" t="inlineStr">
+      <c r="M5" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –林
 姑</t>
         </is>
       </c>
-      <c r="O5" s="10" t="inlineStr">
+      <c r="O5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">당</t>
         </is>
@@ -4186,71 +4227,71 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="24"/>
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J6" s="18" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꼭</t>
         </is>
       </c>
-      <c r="L6" s="18" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰潢</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –潢南</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
@@ -4258,79 +4299,79 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">지화</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –汰潢</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">건</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –汰潢</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">좋은</t>
         </is>
       </c>
-      <c r="J7" s="18" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –汰黃汰</t>
         </is>
       </c>
-      <c r="K7" s="12" t="inlineStr">
+      <c r="K7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">대</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">벗가</t>
         </is>
       </c>
-      <c r="N7" s="18" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –淋
 姑</t>
         </is>
       </c>
-      <c r="O7" s="12" t="inlineStr">
+      <c r="O7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">둥</t>
         </is>
@@ -4338,74 +4379,74 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –潢汰</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">건</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –潢汰潢</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="G8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰潢</t>
         </is>
       </c>
-      <c r="K8" s="13" t="inlineStr">
+      <c r="K8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="L8" s="18" t="inlineStr">
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林林姑</t>
         </is>
       </c>
-      <c r="M8" s="13" t="inlineStr">
+      <c r="M8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">머리</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O8" s="10" t="inlineStr">
+      <c r="O8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">그래</t>
         </is>
@@ -4413,71 +4454,71 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">좋을</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="E9" s="24"/>
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –潢黃</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">온</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢淋淋</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">실안</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –潢</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –潢南</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">당</t>
         </is>
@@ -4485,66 +4526,66 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="25"/>
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="G10" s="25"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林林姑</t>
         </is>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="I10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">듯</t>
         </is>
       </c>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 –淋汰</t>
         </is>
       </c>
-      <c r="K10" s="12" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
-      <c r="L10" s="18" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林林姑</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr">
+      <c r="M10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">갈</t>
         </is>
       </c>
-      <c r="N10" s="18" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –淋汰</t>
         </is>
       </c>
-      <c r="O10" s="12" t="inlineStr">
+      <c r="O10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
@@ -4552,67 +4593,67 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="27"/>
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="27"/>
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –姑</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">맛</t>
         </is>
       </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –汰汰</t>
         </is>
       </c>
-      <c r="K11" s="13" t="inlineStr">
+      <c r="K11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">거</t>
         </is>
       </c>
-      <c r="N11" s="18" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –淋潢</t>
         </is>
       </c>
-      <c r="O11" s="13" t="inlineStr">
+      <c r="O11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">두당</t>
         </is>
@@ -4620,61 +4661,61 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="24"/>
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–汰</t>
         </is>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="24"/>
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–汰</t>
         </is>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="G12" s="24"/>
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="J12" s="18" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰潢</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">둣만</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –姑</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="N12" s="18" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰黃</t>
         </is>
       </c>
-      <c r="O12" s="11" t="inlineStr">
+      <c r="O12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
@@ -4682,62 +4723,62 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="25"/>
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="25"/>
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="25"/>
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">둣</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">둣</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="N13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="O13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">연자</t>
         </is>
@@ -4745,63 +4786,63 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="27"/>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="G14" s="27"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="K14" s="10" t="inlineStr">
+      <c r="K14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="L14" s="18" t="inlineStr">
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="M14" s="13" t="inlineStr">
+      <c r="M14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="N14" s="18" t="inlineStr">
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O14" s="13" t="inlineStr">
+      <c r="O14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">버리고</t>
         </is>

--- a/sheets/민요/검수/는실 타령.xlsx
+++ b/sheets/민요/검수/는실 타령.xlsx
@@ -3958,26 +3958,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3998,12 +3998,12 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃黃
-·</t>
+–</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -4057,7 +4057,7 @@
       <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-··</t>
+––</t>
         </is>
       </c>
       <c r="M3" s="24" t="inlineStr">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>

--- a/sheets/민요/검수/는실 타령.xlsx
+++ b/sheets/민요/검수/는실 타령.xlsx
@@ -4008,7 +4008,8 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">얼씨</t>
+          <t xml:space="preserve">얼
+씨</t>
         </is>
       </c>
       <c r="D3" s="21" t="inlineStr">
@@ -4040,7 +4041,8 @@
       </c>
       <c r="I3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">희오</t>
+          <t xml:space="preserve">희
+오</t>
         </is>
       </c>
       <c r="J3" s="23" t="inlineStr">
@@ -4147,7 +4149,8 @@
       </c>
       <c r="O4" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">그래</t>
+          <t xml:space="preserve">그
+래</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4190,8 @@
       </c>
       <c r="I5" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">사장</t>
+          <t xml:space="preserve">사
+장</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -4306,7 +4310,8 @@
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">지화</t>
+          <t xml:space="preserve">지
+화</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -4339,7 +4344,8 @@
       </c>
       <c r="I7" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">좋은</t>
+          <t xml:space="preserve">좋
+은</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -4361,7 +4367,8 @@
       </c>
       <c r="M7" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">벗가</t>
+          <t xml:space="preserve">벗
+가</t>
         </is>
       </c>
       <c r="N7" s="21" t="inlineStr">
@@ -4438,7 +4445,8 @@
       </c>
       <c r="M8" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">머리</t>
+          <t xml:space="preserve">머
+리</t>
         </is>
       </c>
       <c r="N8" s="23" t="inlineStr">
@@ -4448,7 +4456,8 @@
       </c>
       <c r="O8" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">그래</t>
+          <t xml:space="preserve">그
+래</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4470,8 @@
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">좋을</t>
+          <t xml:space="preserve">좋
+을</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -4498,7 +4508,8 @@
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">실안</t>
+          <t xml:space="preserve">실
+안</t>
         </is>
       </c>
       <c r="L9" s="23" t="inlineStr">
@@ -4655,7 +4666,8 @@
       </c>
       <c r="O11" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">두당</t>
+          <t xml:space="preserve">두
+당</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4708,8 @@
       </c>
       <c r="K12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">둣만</t>
+          <t xml:space="preserve">둣
+만</t>
         </is>
       </c>
       <c r="L12" s="23" t="inlineStr">
@@ -4780,7 +4793,8 @@
       </c>
       <c r="O13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">연자</t>
+          <t xml:space="preserve">연
+자</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4858,9 @@
       </c>
       <c r="O14" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">버리고</t>
+          <t xml:space="preserve">버
+리
+고</t>
         </is>
       </c>
     </row>
